--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00907-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00907-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39A478E9-D45C-472E-AC9A-8B2DF49F23EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41E3370A-38BB-4883-B72F-978EF19BBE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{2C263A7B-D51A-4FD1-A2D3-349C97411ED0}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{BE7AD6F0-EDA3-46B5-9B14-17164440C92C}"/>
   </bookViews>
   <sheets>
     <sheet name="00907-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1720,25 +1720,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9E70A55-73B8-4B3A-B1C1-3847134ADD20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93554F68-B007-4B6D-A128-29A7F617D3F9}">
   <dimension ref="A1:R74"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="8.21875" customWidth="1"/>
-    <col min="5" max="5" width="7.88671875" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" customWidth="1"/>
-    <col min="7" max="9" width="7.88671875" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" customWidth="1"/>
-    <col min="11" max="13" width="7.88671875" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" customWidth="1"/>
-    <col min="15" max="17" width="7.88671875" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -1766,7 +1766,7 @@
       <c r="Q1" s="34"/>
       <c r="R1" s="26"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -1796,7 +1796,7 @@
       <c r="Q2" s="36"/>
       <c r="R2" s="37"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
         <v>2</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="29"/>
       <c r="B4" s="30"/>
       <c r="C4" s="7"/>
@@ -1892,7 +1892,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>2026</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>6.05</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="44"/>
       <c r="C6" s="46"/>
@@ -1972,7 +1972,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="45" t="s">
         <v>27</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="51"/>
       <c r="B8" s="51"/>
       <c r="C8" s="16" t="s">
@@ -2050,7 +2050,7 @@
       <c r="Q8" s="52"/>
       <c r="R8" s="52"/>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="46"/>
       <c r="B9" s="46"/>
       <c r="C9" s="17" t="s">
@@ -2072,7 +2072,7 @@
       <c r="Q9" s="48"/>
       <c r="R9" s="48"/>
     </row>
-    <row r="10" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="57">
         <v>2025</v>
       </c>
@@ -2126,7 +2126,7 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="59" t="s">
         <v>27</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="60"/>
       <c r="B12" s="60"/>
       <c r="C12" s="23" t="s">
@@ -2204,7 +2204,7 @@
       <c r="Q12" s="63"/>
       <c r="R12" s="63"/>
     </row>
-    <row r="13" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="61"/>
       <c r="B13" s="61"/>
       <c r="C13" s="24" t="s">
@@ -2226,7 +2226,7 @@
       <c r="Q13" s="64"/>
       <c r="R13" s="64"/>
     </row>
-    <row r="14" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="59" t="s">
         <v>27</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="60"/>
       <c r="B15" s="60"/>
       <c r="C15" s="23" t="s">
@@ -2304,7 +2304,7 @@
       <c r="Q15" s="63"/>
       <c r="R15" s="63"/>
     </row>
-    <row r="16" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="61"/>
       <c r="B16" s="61"/>
       <c r="C16" s="24" t="s">
@@ -2326,7 +2326,7 @@
       <c r="Q16" s="64"/>
       <c r="R16" s="64"/>
     </row>
-    <row r="17" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="59" t="s">
         <v>27</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="60"/>
       <c r="B18" s="60"/>
       <c r="C18" s="23" t="s">
@@ -2404,7 +2404,7 @@
       <c r="Q18" s="63"/>
       <c r="R18" s="63"/>
     </row>
-    <row r="19" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="61"/>
       <c r="C19" s="24" t="s">
@@ -2426,7 +2426,7 @@
       <c r="Q19" s="64"/>
       <c r="R19" s="64"/>
     </row>
-    <row r="20" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="59" t="s">
         <v>27</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="60"/>
       <c r="B21" s="60"/>
       <c r="C21" s="23" t="s">
@@ -2504,7 +2504,7 @@
       <c r="Q21" s="63"/>
       <c r="R21" s="63"/>
     </row>
-    <row r="22" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="61"/>
       <c r="B22" s="61"/>
       <c r="C22" s="24" t="s">
@@ -2526,7 +2526,7 @@
       <c r="Q22" s="64"/>
       <c r="R22" s="64"/>
     </row>
-    <row r="23" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="59" t="s">
         <v>27</v>
       </c>
@@ -2582,7 +2582,7 @@
         <v>0.68</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="60"/>
       <c r="B24" s="60"/>
       <c r="C24" s="23" t="s">
@@ -2604,7 +2604,7 @@
       <c r="Q24" s="63"/>
       <c r="R24" s="63"/>
     </row>
-    <row r="25" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="61"/>
       <c r="B25" s="61"/>
       <c r="C25" s="24" t="s">
@@ -2626,7 +2626,7 @@
       <c r="Q25" s="64"/>
       <c r="R25" s="64"/>
     </row>
-    <row r="26" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="59" t="s">
         <v>27</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="60"/>
       <c r="B27" s="60"/>
       <c r="C27" s="23" t="s">
@@ -2704,7 +2704,7 @@
       <c r="Q27" s="63"/>
       <c r="R27" s="63"/>
     </row>
-    <row r="28" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="61"/>
       <c r="B28" s="61"/>
       <c r="C28" s="24" t="s">
@@ -2726,7 +2726,7 @@
       <c r="Q28" s="64"/>
       <c r="R28" s="64"/>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="71">
         <v>2024</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="45" t="s">
         <v>27</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="51"/>
       <c r="B31" s="51"/>
       <c r="C31" s="16" t="s">
@@ -2858,7 +2858,7 @@
       <c r="Q31" s="52"/>
       <c r="R31" s="52"/>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="46"/>
       <c r="B32" s="46"/>
       <c r="C32" s="17" t="s">
@@ -2880,7 +2880,7 @@
       <c r="Q32" s="48"/>
       <c r="R32" s="48"/>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="45" t="s">
         <v>27</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="51"/>
       <c r="B34" s="51"/>
       <c r="C34" s="16" t="s">
@@ -2958,7 +2958,7 @@
       <c r="Q34" s="52"/>
       <c r="R34" s="52"/>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="46"/>
       <c r="B35" s="46"/>
       <c r="C35" s="17" t="s">
@@ -2980,7 +2980,7 @@
       <c r="Q35" s="48"/>
       <c r="R35" s="48"/>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="45" t="s">
         <v>27</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="51"/>
       <c r="B37" s="51"/>
       <c r="C37" s="16" t="s">
@@ -3058,7 +3058,7 @@
       <c r="Q37" s="52"/>
       <c r="R37" s="52"/>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="46"/>
       <c r="B38" s="46"/>
       <c r="C38" s="17" t="s">
@@ -3080,7 +3080,7 @@
       <c r="Q38" s="48"/>
       <c r="R38" s="48"/>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="45" t="s">
         <v>27</v>
       </c>
@@ -3136,7 +3136,7 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="51"/>
       <c r="B40" s="51"/>
       <c r="C40" s="16" t="s">
@@ -3158,7 +3158,7 @@
       <c r="Q40" s="52"/>
       <c r="R40" s="52"/>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="46"/>
       <c r="B41" s="46"/>
       <c r="C41" s="17" t="s">
@@ -3180,7 +3180,7 @@
       <c r="Q41" s="48"/>
       <c r="R41" s="48"/>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="45" t="s">
         <v>27</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51"/>
       <c r="B43" s="51"/>
       <c r="C43" s="16" t="s">
@@ -3258,7 +3258,7 @@
       <c r="Q43" s="52"/>
       <c r="R43" s="52"/>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="46"/>
       <c r="B44" s="46"/>
       <c r="C44" s="17" t="s">
@@ -3280,7 +3280,7 @@
       <c r="Q44" s="48"/>
       <c r="R44" s="48"/>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="45" t="s">
         <v>27</v>
       </c>
@@ -3336,7 +3336,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="51"/>
       <c r="B46" s="51"/>
       <c r="C46" s="16" t="s">
@@ -3358,7 +3358,7 @@
       <c r="Q46" s="52"/>
       <c r="R46" s="52"/>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="46"/>
       <c r="B47" s="46"/>
       <c r="C47" s="17" t="s">
@@ -3380,7 +3380,7 @@
       <c r="Q47" s="48"/>
       <c r="R47" s="48"/>
     </row>
-    <row r="48" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="57">
         <v>2023</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="59" t="s">
         <v>27</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="60"/>
       <c r="B50" s="60"/>
       <c r="C50" s="23" t="s">
@@ -3512,7 +3512,7 @@
       <c r="Q50" s="63"/>
       <c r="R50" s="63"/>
     </row>
-    <row r="51" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="61"/>
       <c r="B51" s="61"/>
       <c r="C51" s="24" t="s">
@@ -3534,7 +3534,7 @@
       <c r="Q51" s="64"/>
       <c r="R51" s="64"/>
     </row>
-    <row r="52" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="59" t="s">
         <v>27</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="60"/>
       <c r="B53" s="60"/>
       <c r="C53" s="23" t="s">
@@ -3612,7 +3612,7 @@
       <c r="Q53" s="63"/>
       <c r="R53" s="63"/>
     </row>
-    <row r="54" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="61"/>
       <c r="B54" s="61"/>
       <c r="C54" s="24" t="s">
@@ -3634,7 +3634,7 @@
       <c r="Q54" s="64"/>
       <c r="R54" s="64"/>
     </row>
-    <row r="55" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="59" t="s">
         <v>27</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="60"/>
       <c r="B56" s="60"/>
       <c r="C56" s="23" t="s">
@@ -3712,7 +3712,7 @@
       <c r="Q56" s="63"/>
       <c r="R56" s="63"/>
     </row>
-    <row r="57" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="61"/>
       <c r="B57" s="61"/>
       <c r="C57" s="24" t="s">
@@ -3734,7 +3734,7 @@
       <c r="Q57" s="64"/>
       <c r="R57" s="64"/>
     </row>
-    <row r="58" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="59" t="s">
         <v>27</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="60"/>
       <c r="B59" s="60"/>
       <c r="C59" s="23" t="s">
@@ -3812,7 +3812,7 @@
       <c r="Q59" s="63"/>
       <c r="R59" s="63"/>
     </row>
-    <row r="60" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="61"/>
       <c r="B60" s="61"/>
       <c r="C60" s="24" t="s">
@@ -3834,7 +3834,7 @@
       <c r="Q60" s="64"/>
       <c r="R60" s="64"/>
     </row>
-    <row r="61" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="59" t="s">
         <v>27</v>
       </c>
@@ -3890,7 +3890,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="62" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="60"/>
       <c r="B62" s="60"/>
       <c r="C62" s="23" t="s">
@@ -3912,7 +3912,7 @@
       <c r="Q62" s="63"/>
       <c r="R62" s="63"/>
     </row>
-    <row r="63" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="61"/>
       <c r="B63" s="61"/>
       <c r="C63" s="24" t="s">
@@ -3934,7 +3934,7 @@
       <c r="Q63" s="64"/>
       <c r="R63" s="64"/>
     </row>
-    <row r="64" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="59" t="s">
         <v>27</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="65" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="60"/>
       <c r="B65" s="60"/>
       <c r="C65" s="23" t="s">
@@ -4012,7 +4012,7 @@
       <c r="Q65" s="63"/>
       <c r="R65" s="63"/>
     </row>
-    <row r="66" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="61"/>
       <c r="B66" s="61"/>
       <c r="C66" s="24" t="s">
@@ -4034,7 +4034,7 @@
       <c r="Q66" s="64"/>
       <c r="R66" s="64"/>
     </row>
-    <row r="67" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="71">
         <v>2022</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="45" t="s">
         <v>27</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="51"/>
       <c r="B69" s="51"/>
       <c r="C69" s="16" t="s">
@@ -4166,7 +4166,7 @@
       <c r="Q69" s="52"/>
       <c r="R69" s="52"/>
     </row>
-    <row r="70" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="46"/>
       <c r="B70" s="46"/>
       <c r="C70" s="17" t="s">
@@ -4188,7 +4188,7 @@
       <c r="Q70" s="48"/>
       <c r="R70" s="48"/>
     </row>
-    <row r="71" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="45" t="s">
         <v>27</v>
       </c>
@@ -4244,7 +4244,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="72" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="51"/>
       <c r="B72" s="51"/>
       <c r="C72" s="16" t="s">
@@ -4266,7 +4266,7 @@
       <c r="Q72" s="52"/>
       <c r="R72" s="52"/>
     </row>
-    <row r="73" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="46"/>
       <c r="B73" s="46"/>
       <c r="C73" s="17" t="s">
@@ -4288,7 +4288,7 @@
       <c r="Q73" s="48"/>
       <c r="R73" s="48"/>
     </row>
-    <row r="74" spans="1:18" s="18" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" s="18" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="57" t="s">
         <v>91</v>
       </c>
